--- a/business_forms/037_design_thinking_toolkit_requisition_form--business_forms.xlsx
+++ b/business_forms/037_design_thinking_toolkit_requisition_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1162,8 +1162,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'member1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'member1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'member2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'member2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'member3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'member3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option1':_'tool1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option1': 'tool1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option2':_'tool2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option2': 'tool2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option3':_'tool3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option3': 'tool3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option1':_'platform1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option1': 'platform1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option2':_'platform2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option2': 'platform2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option3':_'platform3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option3': 'platform3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option1':_'manager1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option1': 'manager1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option2':_'manager2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option2': 'manager2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option3':_'manager3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option3': 'manager3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option1':_'lead1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option1': 'lead1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option2':_'lead2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option2': 'lead2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option3':_'lead3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option3': 'lead3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option1':_'low'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option1': 'low'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option2':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option2': 'medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option3':_'high'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option3': 'high'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option1':_'team1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option1': 'team1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option2':_'team2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option2': 'team2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option3':_'team3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option3': 'team3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option1':_'completed'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option1': 'completed'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option2':_'not_completed'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option2': 'not_completed'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option3':_'in_progress'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option3': 'in_progress'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option1':_'active'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option1': 'active'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option2':_'inactive'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option2': 'inactive'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option3':_'on_hold'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option3': 'on_hold'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option1':_'reviewed'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option1': 'reviewed'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option2':_'not_reviewed'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option2': 'not_reviewed'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option3':_'not_reviewed_yet'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option3': 'not_reviewed_yet'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
